--- a/tools/technical-debt-economics/sample-debt-remediation-plan.xlsx
+++ b/tools/technical-debt-economics/sample-debt-remediation-plan.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19940" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,14 +13,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cost Trajectory" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="\$#,##0"/>
+    <numFmt numFmtId="164" formatCode="$#,##0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
   <fonts count="6">
@@ -33,13 +34,13 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="FF1F4E78"/>
+      <color rgb="001F4E78"/>
       <sz val="14"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="FF1F4E78"/>
+      <color rgb="001F4E78"/>
       <sz val="11"/>
     </font>
     <font>
@@ -54,7 +55,7 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -67,7 +68,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E78"/>
+        <fgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
   </fills>
@@ -81,24 +82,23 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFAAAAAA"/>
+        <color rgb="00AAAAAA"/>
       </left>
       <right style="thin">
-        <color rgb="FFAAAAAA"/>
+        <color rgb="00AAAAAA"/>
       </right>
       <top style="thin">
-        <color rgb="FFAAAAAA"/>
+        <color rgb="00AAAAAA"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFAAAAAA"/>
+        <color rgb="00AAAAAA"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -109,40 +109,39 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <dxfs count="4">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFD9E1F2"/>
+          <fgColor rgb="00F8CBAD"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFE699"/>
+          <fgColor rgb="00FFE699"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF8CBAD"/>
+          <fgColor rgb="00D9E1F2"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFE7E6E6"/>
+          <fgColor rgb="00E7E6E6"/>
         </patternFill>
       </fill>
     </dxf>
@@ -508,14 +507,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Technical Debt Remediation Plan</t>
@@ -581,91 +580,111 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Benefit tail after horizon (years)</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Plan Results</t>
         </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Total items</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Items remediated within horizon</t>
+          <t>Total items</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Items deferred</t>
+          <t>Items remediated within horizon</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Total remediation cost</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>3085000</v>
+          <t>Items deferred</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Total carry cost under plan (NPV)</t>
+          <t>Total remediation cost (nominal)</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>7958207.84315663</v>
+        <v>3085000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Total cost if no action (NPV)</t>
+          <t>Remediation cost (NPV)</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>39659039.2036739</v>
+        <v>2753600.823045267</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>NPV savings from plan</t>
+          <t>Total carry cost under plan (NPV)</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>31700831.3605173</v>
+        <v>8050886.169631248</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Items accepted (do not pay back within the horizon)</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>1</v>
+          <t>Total cost if no action (NPV)</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>39659039.20367391</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>NPV savings from plan</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>28854552.2109974</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>NPV savings inside the horizon</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>28854552.2109974</v>
       </c>
     </row>
   </sheetData>
@@ -680,16 +699,17 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="2"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Year-by-Year Remediation Plan</t>
@@ -745,7 +765,7 @@
         <v>0.7925</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.826666666666667</v>
+        <v>0.8266666666666667</v>
       </c>
     </row>
     <row r="5">
@@ -840,22 +860,23 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="35" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="10"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="60" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>All Remediation Decisions</t>
@@ -885,12 +906,12 @@
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>Priority</t>
+          <t>Priority band</t>
         </is>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>Confidence</t>
+          <t>Band rule</t>
         </is>
       </c>
       <c r="G3" s="7" t="inlineStr">
@@ -924,7 +945,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="42" customHeight="1">
+    <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>OPS-001</t>
@@ -950,8 +971,10 @@
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="8" t="n">
-        <v>0.64408491359137</v>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>H5: fixing it removes 79% of what doing nothing would cost</t>
+        </is>
       </c>
       <c r="G4" s="5" t="n">
         <v>150000</v>
@@ -963,16 +986,16 @@
         <v>4400000</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>18197974.1915186</v>
-      </c>
-      <c r="K4" s="4" t="n"/>
-      <c r="L4" s="9" t="inlineStr">
-        <is>
-          <t>Year 1 remediation of this high-priority item. Assumes 50% of fix-year carry still incurred. NPV savings realized: $18,198K.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="42" customHeight="1">
+        <v>16160937.15448152</v>
+      </c>
+      <c r="K4" s="4" t="inlineStr"/>
+      <c r="L4" s="8" t="inlineStr">
+        <is>
+          <t>Funded in year 1; saves $16,161K NPV versus never fixing it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>SEC-001</t>
@@ -998,8 +1021,10 @@
           <t>High</t>
         </is>
       </c>
-      <c r="F5" s="8" t="n">
-        <v>0.975</v>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>H1: incident probability of 10% a year</t>
+        </is>
       </c>
       <c r="G5" s="5" t="n">
         <v>250000</v>
@@ -1011,16 +1036,16 @@
         <v>800000</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>5786413.55749257</v>
-      </c>
-      <c r="K5" s="4" t="n"/>
-      <c r="L5" s="9" t="inlineStr">
-        <is>
-          <t>Year 1 remediation of this high-priority item. High carry growth (20%). Elevated incident probability (10%). Significant incident exposure ($5.0M). Assumes 50% of fix-year carry still incurred. NPV savings realized: $5,786K.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="42" customHeight="1">
+        <v>5416043.187122195</v>
+      </c>
+      <c r="K5" s="4" t="inlineStr"/>
+      <c r="L5" s="8" t="inlineStr">
+        <is>
+          <t>Funded in year 1; saves $5,416K NPV versus never fixing it. Drivers: carry grows 20% a year, 10% annual incident probability, $5.0M incident exposure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>PEOPLE-001</t>
@@ -1046,8 +1071,10 @@
           <t>High</t>
         </is>
       </c>
-      <c r="F6" s="8" t="n">
-        <v>1</v>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>H1: incident probability of 20% a year</t>
+        </is>
       </c>
       <c r="G6" s="5" t="n">
         <v>400000</v>
@@ -1059,16 +1086,16 @@
         <v>200000</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>2215965.38268777</v>
-      </c>
-      <c r="K6" s="4" t="n"/>
-      <c r="L6" s="9" t="inlineStr">
-        <is>
-          <t>Year 1 remediation of this high-priority item. High carry growth (25%). Elevated incident probability (20%). Significant incident exposure ($2.0M). Assumes 50% of fix-year carry still incurred. NPV savings realized: $2,216K.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
+        <v>2123372.790095179</v>
+      </c>
+      <c r="K6" s="4" t="inlineStr"/>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>Funded in year 1; saves $2,123K NPV versus never fixing it. Drivers: carry grows 25% a year, 20% annual incident probability, $2.0M incident exposure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>IP-001</t>
@@ -1094,8 +1121,10 @@
           <t>High</t>
         </is>
       </c>
-      <c r="F7" s="8" t="n">
-        <v>0.8147123893805309</v>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>H1: incident probability of 10% a year</t>
+        </is>
       </c>
       <c r="G7" s="5" t="n">
         <v>50000</v>
@@ -1107,16 +1136,16 @@
         <v>25000</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>1816490.01158596</v>
-      </c>
-      <c r="K7" s="4" t="n"/>
-      <c r="L7" s="9" t="inlineStr">
-        <is>
-          <t>Year 1 remediation of this high-priority item. Elevated incident probability (10%). Significant incident exposure ($5.0M). Assumes 50% of fix-year carry still incurred. NPV savings realized: $1,816K.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="42" customHeight="1">
+        <v>1804915.93751188</v>
+      </c>
+      <c r="K7" s="4" t="inlineStr"/>
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t>Funded in year 1; saves $1,805K NPV versus never fixing it. Drivers: 10% annual incident probability, $5.0M incident exposure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>OPS-002</t>
@@ -1142,8 +1171,10 @@
           <t>High</t>
         </is>
       </c>
-      <c r="F8" s="8" t="n">
-        <v>0.8607104701265144</v>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>H2: saves 78% of its do-nothing cost, and the cost is growing or incident-driven</t>
+        </is>
       </c>
       <c r="G8" s="5" t="n">
         <v>200000</v>
@@ -1155,16 +1186,16 @@
         <v>100000</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>1660847.57143872</v>
-      </c>
-      <c r="K8" s="4" t="n"/>
-      <c r="L8" s="9" t="inlineStr">
-        <is>
-          <t>Year 1 remediation of this high-priority item. Significant incident exposure ($8.0M). Assumes 50% of fix-year carry still incurred. NPV savings realized: $1,661K.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="42" customHeight="1">
+        <v>1614551.27514242</v>
+      </c>
+      <c r="K8" s="4" t="inlineStr"/>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>Funded in year 1; saves $1,615K NPV versus never fixing it. Drivers: $8.0M incident exposure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>SEC-002</t>
@@ -1190,8 +1221,10 @@
           <t>High</t>
         </is>
       </c>
-      <c r="F9" s="8" t="n">
-        <v>0.9239046746104492</v>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>H2: saves 78% of its do-nothing cost, and the cost is growing or incident-driven</t>
+        </is>
       </c>
       <c r="G9" s="5" t="n">
         <v>80000</v>
@@ -1203,252 +1236,262 @@
         <v>50000</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>731034.384668746</v>
-      </c>
-      <c r="K9" s="4" t="n"/>
-      <c r="L9" s="9" t="inlineStr">
-        <is>
-          <t>Year 1 remediation of this high-priority item. High carry growth (15%). Elevated incident probability (8%). Significant incident exposure ($2.0M). Assumes 50% of fix-year carry still incurred. NPV savings realized: $731K.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1">
+        <v>707886.2365205977</v>
+      </c>
+      <c r="K9" s="4" t="inlineStr"/>
+      <c r="L9" s="8" t="inlineStr">
+        <is>
+          <t>Funded in year 1; saves $708K NPV versus never fixing it. Drivers: carry grows 15% a year, $2.0M incident exposure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>ARCH-001</t>
+          <t>ARCH-002</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Multi-tenancy migration abandoned mid-flight</t>
+          <t>PostgreSQL 11 EOL - upgrade required</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Year 2</t>
+          <t>Year 1</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>H2: saves 59% of its do-nothing cost, and the cost is growing or incident-driven</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>200000</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>50000</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>380285.4058413646</v>
+      </c>
+      <c r="K10" s="4" t="inlineStr"/>
+      <c r="L10" s="8" t="inlineStr">
+        <is>
+          <t>Funded in year 1; saves $380K NPV versus never fixing it. Drivers: carry grows 30% a year, $1.5M incident exposure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>DATA-002</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Three different MAU definitions across teams</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Year 1</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F10" s="8" t="n">
-        <v>0.8887131164487698</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>360</v>
-      </c>
-      <c r="I10" s="5" t="n">
-        <v>392000.0000000001</v>
-      </c>
-      <c r="J10" s="5" t="n">
-        <v>441666.131782722</v>
-      </c>
-      <c r="K10" s="4" t="n"/>
-      <c r="L10" s="9" t="inlineStr">
-        <is>
-          <t>Year 2 remediation of this medium-priority item. Significant incident exposure ($3.0M). Later than its unconstrained best year (1) because of budget, capacity, dependency timing, or the payback rule. Assumes 50% of fix-year carry still incurred. NPV savings realized: $442K.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>ARCH-002</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>PostgreSQL 11 EOL - upgrade required</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>M1: positive savings with no urgency driver</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>120000</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>80000</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>172232.2126390881</v>
+      </c>
+      <c r="K11" s="4" t="inlineStr"/>
+      <c r="L11" s="8" t="inlineStr">
+        <is>
+          <t>Funded in year 1; saves $172K NPV versus never fixing it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>DATA-001</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Customer churn calculation bug</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>Year 1</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>H5: fixing it removes 54% of what doing nothing would cost</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>75000</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>50000</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>138530.4197979374</v>
+      </c>
+      <c r="K12" s="4" t="inlineStr"/>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t>Funded in year 1; saves $139K NPV versus never fixing it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>PROCESS-001</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>No DORA metrics tracking</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Year 1</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F11" s="8" t="n">
-        <v>0.8202862472439368</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>200000</v>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>90</v>
-      </c>
-      <c r="I11" s="5" t="n">
-        <v>50000</v>
-      </c>
-      <c r="J11" s="5" t="n">
-        <v>403433.553989513</v>
-      </c>
-      <c r="K11" s="4" t="n"/>
-      <c r="L11" s="9" t="inlineStr">
-        <is>
-          <t>Year 1 remediation of this medium-priority item. High carry growth (30%). Significant incident exposure ($1.5M). Assumes 50% of fix-year carry still incurred. NPV savings realized: $403K.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>DATA-002</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Three different MAU definitions across teams</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Data</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>Year 1</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="n">
-        <v>0.9166969560074461</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>120000</v>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="I12" s="5" t="n">
-        <v>80000</v>
-      </c>
-      <c r="J12" s="5" t="n">
-        <v>209269.249676125</v>
-      </c>
-      <c r="K12" s="4" t="n"/>
-      <c r="L12" s="9" t="inlineStr">
-        <is>
-          <t>Year 1 remediation of this medium-priority item. Assumes 50% of fix-year carry still incurred. NPV savings realized: $209K.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>DATA-001</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Customer churn calculation bug</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Data</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Year 1</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="n">
-        <v>0.9528441878193218</v>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>M1: positive savings with no urgency driver</t>
+        </is>
       </c>
       <c r="G13" s="5" t="n">
-        <v>75000</v>
+        <v>60000</v>
       </c>
       <c r="H13" s="4" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>161678.567946086</v>
-      </c>
-      <c r="K13" s="4" t="n"/>
-      <c r="L13" s="9" t="inlineStr">
-        <is>
-          <t>Year 1 remediation of this medium-priority item. Assumes 50% of fix-year carry still incurred. NPV savings realized: $162K.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1">
+        <v>62169.86884164329</v>
+      </c>
+      <c r="K13" s="4" t="inlineStr"/>
+      <c r="L13" s="8" t="inlineStr">
+        <is>
+          <t>Funded in year 1; saves $62K NPV versus never fixing it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>PROCESS-001</t>
+          <t>ARCH-001</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>No DORA metrics tracking</t>
+          <t>Multi-tenancy migration abandoned mid-flight</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Year 1</t>
+          <t>Year 2</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="n">
-        <v>0.9085785722397337</v>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>H3: other items depend on it and it is worth doing early</t>
+        </is>
       </c>
       <c r="G14" s="5" t="n">
-        <v>60000</v>
+        <v>1500000</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>30</v>
+        <v>360</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>30000</v>
+        <v>392000.0000000001</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>76058.7577305322</v>
-      </c>
-      <c r="K14" s="4" t="n"/>
-      <c r="L14" s="9" t="inlineStr">
-        <is>
-          <t>Year 1 remediation of this medium-priority item. Assumes 50% of fix-year carry still incurred. NPV savings realized: $76K.</t>
+        <v>273627.7230035714</v>
+      </c>
+      <c r="K14" s="4" t="inlineStr"/>
+      <c r="L14" s="8" t="inlineStr">
+        <is>
+          <t>Funded in year 2; saves $274K NPV versus never fixing it. Its standalone best year is 1, moved to 2 because budget, capacity, or dependencies make that the better portfolio choice. Drivers: $3.0M incident exposure, unblocks ARCH-003.</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1513,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>Not funded</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -1478,8 +1521,10 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="F15" s="8" t="n">
-        <v>0.9834626435963943</v>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>H0: fixing costs more than it saves over the horizon</t>
+        </is>
       </c>
       <c r="G15" s="5" t="n">
         <v>800000</v>
@@ -1488,7 +1533,7 @@
         <v>240</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>150000</v>
+        <v>219615.0000000001</v>
       </c>
       <c r="J15" s="5" t="n">
         <v>0</v>
@@ -1498,27 +1543,27 @@
           <t>ARCH-001</t>
         </is>
       </c>
-      <c r="L15" s="9" t="inlineStr">
-        <is>
-          <t>Accepted, no payback: remediating in any year from 3 to 5 costs more than carrying it (NPV savings are zero or negative in every such year) and no other item depends on it. Carries $840K of NPV cost as a deliberate cost of doing business. Set Accept items that never pay back to 0 on Parameters to force scheduling.</t>
+      <c r="L15" s="8" t="inlineStr">
+        <is>
+          <t>Accepted as carry: fixing it costs more than it saves over the 5-year horizon.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D4:D15">
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
-      <formula>"Deferred"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="E4:E15">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"High"</formula>
     </cfRule>
     <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
       <formula>"Medium"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"Low"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:D15">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
+      <formula>"Not funded"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1532,7 +1577,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -1540,7 +1585,7 @@
     <col width="18" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Cost Trajectory: Plan vs No Action</t>
@@ -1574,13 +1619,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="5" t="n">
-        <v>6213500</v>
+        <v>5187500</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>8547000</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>2333500</v>
+        <v>3359500</v>
       </c>
     </row>
     <row r="5">
@@ -1588,13 +1633,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1981000</v>
+        <v>1891000</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>9207750</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>7226750</v>
+        <v>7316750</v>
       </c>
     </row>
     <row r="6">
@@ -1616,7 +1661,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>229650</v>
+        <v>229650.0000000001</v>
       </c>
       <c r="C7" s="5" t="n">
         <v>10802286.975</v>
@@ -1630,7 +1675,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>249615</v>
+        <v>249615.0000000001</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>11767193.41875</v>

--- a/tools/technical-debt-economics/sample-debt-remediation-plan.xlsx
+++ b/tools/technical-debt-economics/sample-debt-remediation-plan.xlsx
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>8050886.169631248</v>
+        <v>9078046.663458407</v>
       </c>
     </row>
     <row r="18">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>28854552.2109974</v>
+        <v>27827391.71717024</v>
       </c>
     </row>
     <row r="20">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>28854552.2109974</v>
+        <v>27827391.71717023</v>
       </c>
     </row>
   </sheetData>
@@ -986,12 +986,12 @@
         <v>4400000</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>16160937.15448152</v>
+        <v>16160474.19151856</v>
       </c>
       <c r="K4" s="4" t="inlineStr"/>
       <c r="L4" s="8" t="inlineStr">
         <is>
-          <t>Funded in year 1; saves $16,161K NPV versus never fixing it.</t>
+          <t>Funded in year 1; saves $16,160K NPV versus never fixing it.</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
         <v>800000</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>5416043.187122195</v>
+        <v>5184561.705640713</v>
       </c>
       <c r="K5" s="4" t="inlineStr"/>
       <c r="L5" s="8" t="inlineStr">
         <is>
-          <t>Funded in year 1; saves $5,416K NPV versus never fixing it. Drivers: carry grows 20% a year, 10% annual incident probability, $5.0M incident exposure.</t>
+          <t>Funded in year 1; saves $5,185K NPV versus never fixing it. Drivers: carry grows 20% a year, 10% annual incident probability, $5.0M incident exposure.</t>
         </is>
       </c>
     </row>
@@ -1086,12 +1086,12 @@
         <v>200000</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>2123372.790095179</v>
+        <v>1938187.604909994</v>
       </c>
       <c r="K6" s="4" t="inlineStr"/>
       <c r="L6" s="8" t="inlineStr">
         <is>
-          <t>Funded in year 1; saves $2,123K NPV versus never fixing it. Drivers: carry grows 25% a year, 20% annual incident probability, $2.0M incident exposure.</t>
+          <t>Funded in year 1; saves $1,938K NPV versus never fixing it. Drivers: carry grows 25% a year, 20% annual incident probability, $2.0M incident exposure.</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1136,12 @@
         <v>25000</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>1804915.93751188</v>
+        <v>1573434.456030398</v>
       </c>
       <c r="K7" s="4" t="inlineStr"/>
       <c r="L7" s="8" t="inlineStr">
         <is>
-          <t>Funded in year 1; saves $1,805K NPV versus never fixing it. Drivers: 10% annual incident probability, $5.0M incident exposure.</t>
+          <t>Funded in year 1; saves $1,573K NPV versus never fixing it. Drivers: 10% annual incident probability, $5.0M incident exposure.</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>H2: saves 78% of its do-nothing cost, and the cost is growing or incident-driven</t>
+          <t>H2: saves 69% of its do-nothing cost, and the cost is growing or incident-driven</t>
         </is>
       </c>
       <c r="G8" s="5" t="n">
@@ -1186,12 +1186,12 @@
         <v>100000</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>1614551.27514242</v>
+        <v>1429366.089957235</v>
       </c>
       <c r="K8" s="4" t="inlineStr"/>
       <c r="L8" s="8" t="inlineStr">
         <is>
-          <t>Funded in year 1; saves $1,615K NPV versus never fixing it. Drivers: $8.0M incident exposure.</t>
+          <t>Funded in year 1; saves $1,429K NPV versus never fixing it. Drivers: $8.0M incident exposure.</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>H2: saves 78% of its do-nothing cost, and the cost is growing or incident-driven</t>
+          <t>H2: saves 70% of its do-nothing cost, and the cost is growing or incident-driven</t>
         </is>
       </c>
       <c r="G9" s="5" t="n">
@@ -1236,12 +1236,12 @@
         <v>50000</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>707886.2365205977</v>
+        <v>633812.1624465237</v>
       </c>
       <c r="K9" s="4" t="inlineStr"/>
       <c r="L9" s="8" t="inlineStr">
         <is>
-          <t>Funded in year 1; saves $708K NPV versus never fixing it. Drivers: carry grows 15% a year, $2.0M incident exposure.</t>
+          <t>Funded in year 1; saves $634K NPV versus never fixing it. Drivers: carry grows 15% a year, $2.0M incident exposure.</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>H2: saves 59% of its do-nothing cost, and the cost is growing or incident-driven</t>
+          <t>H2: saves 53% of its do-nothing cost, and the cost is growing or incident-driven</t>
         </is>
       </c>
       <c r="G10" s="5" t="n">
@@ -1286,12 +1286,12 @@
         <v>50000</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>380285.4058413646</v>
+        <v>345563.1836191425</v>
       </c>
       <c r="K10" s="4" t="inlineStr"/>
       <c r="L10" s="8" t="inlineStr">
         <is>
-          <t>Funded in year 1; saves $380K NPV versus never fixing it. Drivers: carry grows 30% a year, $1.5M incident exposure.</t>
+          <t>Funded in year 1; saves $346K NPV versus never fixing it. Drivers: carry grows 30% a year, $1.5M incident exposure.</t>
         </is>
       </c>
     </row>
@@ -1336,12 +1336,12 @@
         <v>80000</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>172232.2126390881</v>
+        <v>171306.2867131622</v>
       </c>
       <c r="K11" s="4" t="inlineStr"/>
       <c r="L11" s="8" t="inlineStr">
         <is>
-          <t>Funded in year 1; saves $172K NPV versus never fixing it.</t>
+          <t>Funded in year 1; saves $171K NPV versus never fixing it.</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>H5: fixing it removes 54% of what doing nothing would cost</t>
+          <t>H5: fixing it removes 52% of what doing nothing would cost</t>
         </is>
       </c>
       <c r="G12" s="5" t="n">
@@ -1386,12 +1386,12 @@
         <v>50000</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>138530.4197979374</v>
+        <v>133900.7901683078</v>
       </c>
       <c r="K12" s="4" t="inlineStr"/>
       <c r="L12" s="8" t="inlineStr">
         <is>
-          <t>Funded in year 1; saves $139K NPV versus never fixing it.</t>
+          <t>Funded in year 1; saves $134K NPV versus never fixing it.</t>
         </is>
       </c>
     </row>
@@ -1436,12 +1436,12 @@
         <v>30000</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>62169.86884164329</v>
+        <v>60318.01698979143</v>
       </c>
       <c r="K13" s="4" t="inlineStr"/>
       <c r="L13" s="8" t="inlineStr">
         <is>
-          <t>Funded in year 1; saves $62K NPV versus never fixing it.</t>
+          <t>Funded in year 1; saves $60K NPV versus never fixing it.</t>
         </is>
       </c>
     </row>
@@ -1486,12 +1486,12 @@
         <v>392000.0000000001</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>273627.7230035714</v>
+        <v>196467.2291764109</v>
       </c>
       <c r="K14" s="4" t="inlineStr"/>
       <c r="L14" s="8" t="inlineStr">
         <is>
-          <t>Funded in year 2; saves $274K NPV versus never fixing it. Its standalone best year is 1, moved to 2 because budget, capacity, or dependencies make that the better portfolio choice. Drivers: $3.0M incident exposure, unblocks ARCH-003.</t>
+          <t>Funded in year 2; saves $196K NPV versus never fixing it. Its standalone best year is 1, moved to 2 because budget, capacity, or dependencies make that the better portfolio choice. Drivers: $3.0M incident exposure, unblocks ARCH-003.</t>
         </is>
       </c>
     </row>
@@ -1619,13 +1619,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="5" t="n">
-        <v>5187500</v>
+        <v>10132000</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>8547000</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>3359500</v>
+        <v>-1585000</v>
       </c>
     </row>
     <row r="5">
@@ -1633,13 +1633,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1891000</v>
+        <v>2267000</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>9207750</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>7316750</v>
+        <v>6940750</v>
       </c>
     </row>
     <row r="6">
